--- a/vlearn-app/public/quiz_excel/Day_08_RAG Pipeline _ Retrieval Evaluation/Day_08_Phan_03_19_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_08_RAG Pipeline _ Retrieval Evaluation/Day_08_Phan_03_19_Cau.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o4 → o3 → o1</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -695,7 +695,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không thể sửa để bám bằng chứng nếu chưa xác định mệnh đề nào thiếu hỗ trợ.</t>
+          <t>Quy trình tự sửa chữa bản nháp (self-correction workflow) bám sát bằng chứng: 1. Tách bản nháp thành các mệnh đề nguyên tử độc lập (o2) -&gt; 2. So sánh từng mệnh đề với context và gắn nhãn được hỗ trợ/mâu thuẫn/chưa có bằng chứng (o4) -&gt; 3. Áp dụng thao tác bỏ, sửa hoặc thử lại có giới hạn đối với mệnh đề chưa đạt (o3) -&gt; 4. Xuất câu trả lời cuối cùng hoặc thông báo từ chối trả lời (abstain) (o1).</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -942,7 +942,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một trường hợp không gắn với bằng chứng sẽ không giúp xác định lỗi hồi quy nằm ở retrieval hay generation.</t>
+          <t>Để xây dựng một trường hợp kiểm thử hồi quy RAG (regression test fixture) có thể tái lập từ log sự cố, bản ghi kiểm thử bắt buộc phải có: (a) Câu hỏi đầu vào; (b) Đáp án chuẩn hoặc phạm vi đáp án cho phép; (c) Nguồn tài liệu hoặc chunk evidence kỳ vọng; (d) Khả năng trả lời (answerability label); (e) Độ khó và phân loại lỗi; (f) Định danh người đánh giá và phiên bản kiểm thử.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -1451,7 +1451,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tồn tại và hỗ trợ là hai điều kiện độc lập.</t>
+          <t>Khi mệnh đề trích dẫn [D3] nhưng đoạn trích D3 không nêu con số mà mệnh đề khẳng định, trong khi D4 lại chứa con số đó: (a) Loại bỏ D3 vì không hỗ trợ dữ kiện con số; (b) Dùng D4 nếu D4 thực sự hỗ trợ đầy đủ mệnh đề; (c) Đặt citation gắn liền ngay mệnh đề nguyên tử chứa con số; (e) Nếu không có tài liệu nào hỗ trợ thì phải sửa, bỏ hoặc từ chối trả lời (abstain) ở mệnh đề đó. Tuyệt đối không giữ D3 chỉ vì ID có tồn tại.</t>
         </is>
       </c>
     </row>
